--- a/data/trans_orig/P71_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P71_R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2007</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2007 (tasa de respuesta: 98,33%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>275674</t>
+          <t>272195</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>335133</t>
+          <t>333262</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>26,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>482695</t>
+          <t>482314</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>548500</t>
+          <t>552293</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>770595</t>
+          <t>771554</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>863394</t>
+          <t>862116</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,59%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>675137</t>
+          <t>677008</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>734596</t>
+          <t>738075</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>73,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>734946</t>
+          <t>731153</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>800751</t>
+          <t>801132</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1430322</t>
+          <t>1431600</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1523121</t>
+          <t>1522162</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>66,36%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>217490</t>
+          <t>214094</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>274993</t>
+          <t>272942</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>320751</t>
+          <t>318012</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>387494</t>
+          <t>385215</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>549446</t>
+          <t>552637</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>637779</t>
+          <t>644890</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,93%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1398866</t>
+          <t>1400917</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1456369</t>
+          <t>1459765</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1174398</t>
+          <t>1176677</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1241141</t>
+          <t>1243880</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2597972</t>
+          <t>2590861</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2686305</t>
+          <t>2683114</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,02%</t>
+          <t>82,92%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26995</t>
+          <t>27003</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52582</t>
+          <t>51938</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43939</t>
+          <t>42708</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>73811</t>
+          <t>72687</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76028</t>
+          <t>75279</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>115360</t>
+          <t>116377</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,45%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>494118</t>
+          <t>494762</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>519705</t>
+          <t>519697</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>395820</t>
+          <t>396944</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>425692</t>
+          <t>426923</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,28%</t>
+          <t>84,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>900971</t>
+          <t>899954</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>940303</t>
+          <t>941052</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,59%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>536405</t>
+          <t>542936</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>626782</t>
+          <t>627470</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,6%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>873035</t>
+          <t>873730</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>977713</t>
+          <t>977973</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,49%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1429935</t>
+          <t>1443179</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1569869</t>
+          <t>1577379</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>24,1%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2604047</t>
+          <t>2603359</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2694424</t>
+          <t>2687893</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2337256</t>
+          <t>2336996</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2441934</t>
+          <t>2441239</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>73,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4975929</t>
+          <t>4968419</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5115863</t>
+          <t>5102619</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>76,02%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>77,95%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2012</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2012 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>364392</t>
+          <t>361493</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>425762</t>
+          <t>424807</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,64%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>447135</t>
+          <t>449906</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>519306</t>
+          <t>517913</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>831869</t>
+          <t>826598</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>926416</t>
+          <t>923018</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>40,16%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>542319</t>
+          <t>543274</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>603689</t>
+          <t>606588</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,36%</t>
+          <t>62,66%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>811055</t>
+          <t>812448</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>883226</t>
+          <t>880455</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,39%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1372026</t>
+          <t>1375424</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1466573</t>
+          <t>1471844</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>59,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>64,04%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>547948</t>
+          <t>549366</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>632296</t>
+          <t>631463</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>528110</t>
+          <t>526491</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>608084</t>
+          <t>610175</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1094335</t>
+          <t>1100815</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1210694</t>
+          <t>1215731</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>32,77%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1326542</t>
+          <t>1327375</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1410890</t>
+          <t>1409472</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1142502</t>
+          <t>1140411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1222476</t>
+          <t>1224095</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2498730</t>
+          <t>2493693</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2615089</t>
+          <t>2608609</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,32%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>43409</t>
+          <t>44713</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75176</t>
+          <t>74502</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53107</t>
+          <t>53327</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84120</t>
+          <t>84871</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>105166</t>
+          <t>104439</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>150104</t>
+          <t>149917</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>400053</t>
+          <t>400727</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>431820</t>
+          <t>430516</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,18%</t>
+          <t>84,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>373576</t>
+          <t>372825</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>404589</t>
+          <t>404369</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,62%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>782821</t>
+          <t>783008</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>827759</t>
+          <t>828486</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,73%</t>
+          <t>88,81%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>986910</t>
+          <t>990155</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1097969</t>
+          <t>1104671</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1062526</t>
+          <t>1062824</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1174305</t>
+          <t>1180451</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3420,7 +3420,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>33,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2080255</t>
+          <t>2081987</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2241161</t>
+          <t>2236096</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,97%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,29%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2304179</t>
+          <t>2297477</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2415238</t>
+          <t>2411993</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2364338</t>
+          <t>2358192</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2476117</t>
+          <t>2475819</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,7 +3528,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>66,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4699630</t>
+          <t>4704695</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4860536</t>
+          <t>4858804</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,71%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,03%</t>
+          <t>70,0%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2016</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2016 (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>329165</t>
+          <t>329806</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>380755</t>
+          <t>384303</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,05%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>457343</t>
+          <t>460805</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>524259</t>
+          <t>523781</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>52,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>808052</t>
+          <t>805045</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>890837</t>
+          <t>890663</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>51,31%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>366543</t>
+          <t>362995</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>418133</t>
+          <t>417492</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>48,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,95%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>464211</t>
+          <t>464689</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>531127</t>
+          <t>527665</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,96%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,73%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>844932</t>
+          <t>845106</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>927717</t>
+          <t>930724</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,68%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,62%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>664721</t>
+          <t>659751</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>751674</t>
+          <t>751421</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>643680</t>
+          <t>647347</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>729360</t>
+          <t>731035</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,55%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,88%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1332757</t>
+          <t>1327479</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1458875</t>
+          <t>1459300</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,15%</t>
+          <t>36,16%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1306598</t>
+          <t>1306851</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1393551</t>
+          <t>1398521</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1248444</t>
+          <t>1246769</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1334124</t>
+          <t>1330457</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,45%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2577202</t>
+          <t>2576777</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2703320</t>
+          <t>2708598</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,85%</t>
+          <t>63,84%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,11%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44663</t>
+          <t>44998</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76382</t>
+          <t>76176</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62077</t>
+          <t>60957</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>94666</t>
+          <t>93692</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114286</t>
+          <t>115871</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>158863</t>
+          <t>159996</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,64%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>468597</t>
+          <t>468803</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>500316</t>
+          <t>499981</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>85,98%</t>
+          <t>86,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>453410</t>
+          <t>454384</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>485999</t>
+          <t>487119</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>934192</t>
+          <t>933059</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>978769</t>
+          <t>977184</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>85,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,54%</t>
+          <t>89,4%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1063194</t>
+          <t>1062183</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1175195</t>
+          <t>1172666</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1200047</t>
+          <t>1197515</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1319981</t>
+          <t>1313839</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2297526</t>
+          <t>2292824</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2456657</t>
+          <t>2451188</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,71%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2175355</t>
+          <t>2177884</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2287356</t>
+          <t>2288367</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,27%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2194370</t>
+          <t>2200512</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2314304</t>
+          <t>2316836</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>62,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4408244</t>
+          <t>4413713</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4567375</t>
+          <t>4572077</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>64,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,6%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2023</t>
+          <t>Población que llega a fin de mes con dificultad o mucha dificultad en 2023 (tasa de respuesta: 98,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>118016</t>
+          <t>117461</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154657</t>
+          <t>154640</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,39%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>183743</t>
+          <t>184883</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>224709</t>
+          <t>223749</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>310738</t>
+          <t>311551</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>364734</t>
+          <t>366728</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,39%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>349988</t>
+          <t>350005</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>386629</t>
+          <t>387184</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,61%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>518333</t>
+          <t>519293</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>559299</t>
+          <t>558159</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,76%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>882953</t>
+          <t>880959</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>936949</t>
+          <t>936136</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,03%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>188045</t>
+          <t>178814</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>311332</t>
+          <t>311258</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -5915,17 +5915,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>371002</t>
+          <t>371003</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>287690</t>
+          <t>283945</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>564842</t>
+          <t>577725</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>26,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>519129</t>
+          <t>518905</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>805441</t>
+          <t>852269</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5975,7 +5975,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>19,13%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1950824</t>
+          <t>1950898</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2074111</t>
+          <t>2083342</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6018,7 +6018,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>91,69%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1628729</t>
+          <t>1615847</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1905881</t>
+          <t>1909627</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>73,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3650287</t>
+          <t>3603459</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3936599</t>
+          <t>3936823</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,7 +6083,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>80,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2193571</t>
+          <t>2193572</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2193571</t>
+          <t>2193572</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2193571</t>
+          <t>2193572</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10389</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28678</t>
+          <t>29286</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>24462</t>
+          <t>25511</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46587</t>
+          <t>45616</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39188</t>
+          <t>38771</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66830</t>
+          <t>65834</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>614140</t>
+          <t>613532</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>632429</t>
+          <t>632890</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>604511</t>
+          <t>605482</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>626636</t>
+          <t>625587</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,84%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1227086</t>
+          <t>1228082</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1254728</t>
+          <t>1255145</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,0%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>319913</t>
+          <t>316599</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>465238</t>
+          <t>465255</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>515613</t>
+          <t>515803</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>828571</t>
+          <t>822901</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>894882</t>
+          <t>890887</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1223001</t>
+          <t>1208023</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,26%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2944382</t>
+          <t>2944365</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3089707</t>
+          <t>3093021</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2759141</t>
+          <t>2764811</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3072099</t>
+          <t>3071909</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5774330</t>
+          <t>5789308</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6102449</t>
+          <t>6106444</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,27%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P71_R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P71_R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>272195</t>
+          <t>273614</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>333262</t>
+          <t>331729</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>482314</t>
+          <t>481911</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>552293</t>
+          <t>549111</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>37,58%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>42,78%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>771554</t>
+          <t>775483</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>862116</t>
+          <t>867180</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>33,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,59%</t>
+          <t>37,81%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>677008</t>
+          <t>678541</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>738075</t>
+          <t>736656</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>731153</t>
+          <t>734335</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>801132</t>
+          <t>801535</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1431600</t>
+          <t>1426536</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1522162</t>
+          <t>1518233</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,41%</t>
+          <t>62,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>66,19%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>214094</t>
+          <t>216808</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>272942</t>
+          <t>276715</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>318012</t>
+          <t>317829</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>385215</t>
+          <t>385099</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>552637</t>
+          <t>552467</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>644890</t>
+          <t>640793</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,93%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1400917</t>
+          <t>1397144</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1459765</t>
+          <t>1457051</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1176677</t>
+          <t>1176793</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1243880</t>
+          <t>1244063</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2590861</t>
+          <t>2594958</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2683114</t>
+          <t>2683284</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>82,93%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27003</t>
+          <t>26020</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51938</t>
+          <t>51243</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42708</t>
+          <t>43181</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>72687</t>
+          <t>73259</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>75279</t>
+          <t>76385</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>116377</t>
+          <t>115926</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>494762</t>
+          <t>495457</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>519697</t>
+          <t>520680</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>396944</t>
+          <t>396372</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>426923</t>
+          <t>426450</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>899954</t>
+          <t>900405</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>941052</t>
+          <t>939946</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,55%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,48%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>542936</t>
+          <t>539752</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>627470</t>
+          <t>628141</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>873730</t>
+          <t>872523</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>977973</t>
+          <t>974556</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1443179</t>
+          <t>1440326</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1577379</t>
+          <t>1578494</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,11%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2603359</t>
+          <t>2602688</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2687893</t>
+          <t>2691077</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2336996</t>
+          <t>2340413</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2441239</t>
+          <t>2442446</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4968419</t>
+          <t>4967304</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5102619</t>
+          <t>5105472</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,0%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>361493</t>
+          <t>367062</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>424807</t>
+          <t>427636</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>449906</t>
+          <t>448609</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>517913</t>
+          <t>519944</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>826598</t>
+          <t>825877</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>923018</t>
+          <t>923846</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,19%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>543274</t>
+          <t>540445</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>606588</t>
+          <t>601019</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>55,83%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,66%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>812448</t>
+          <t>810417</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>880455</t>
+          <t>881752</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,07%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1375424</t>
+          <t>1374596</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1471844</t>
+          <t>1472565</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,07%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>549366</t>
+          <t>548709</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>631463</t>
+          <t>633015</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>526491</t>
+          <t>528772</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>610175</t>
+          <t>611839</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,21%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>34,86%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1100815</t>
+          <t>1100754</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1215731</t>
+          <t>1214092</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>32,73%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1327375</t>
+          <t>1325823</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1409472</t>
+          <t>1410129</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1140411</t>
+          <t>1138747</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1224095</t>
+          <t>1221814</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,14%</t>
+          <t>65,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,79%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2493693</t>
+          <t>2495332</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2608609</t>
+          <t>2608670</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,33%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44713</t>
+          <t>44343</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74502</t>
+          <t>74713</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53327</t>
+          <t>52177</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>84871</t>
+          <t>85401</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>104439</t>
+          <t>104321</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>149917</t>
+          <t>145747</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,62%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>400727</t>
+          <t>400516</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>430516</t>
+          <t>430886</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,28%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>372825</t>
+          <t>372295</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>404369</t>
+          <t>405519</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>783008</t>
+          <t>787178</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>828486</t>
+          <t>828604</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,82%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>990155</t>
+          <t>983184</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1104671</t>
+          <t>1096749</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,47%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1062824</t>
+          <t>1062463</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1180451</t>
+          <t>1173717</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2081987</t>
+          <t>2075894</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2236096</t>
+          <t>2237303</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>32,23%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2297477</t>
+          <t>2305399</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2411993</t>
+          <t>2418964</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>71,1%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2358192</t>
+          <t>2364926</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2475819</t>
+          <t>2476180</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>69,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4704695</t>
+          <t>4703488</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4858804</t>
+          <t>4864897</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,78%</t>
+          <t>67,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>70,09%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>329806</t>
+          <t>326161</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>384303</t>
+          <t>380249</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,43%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>460805</t>
+          <t>459205</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>523781</t>
+          <t>523435</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>52,99%</t>
+          <t>52,95%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>805045</t>
+          <t>803009</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>890663</t>
+          <t>885203</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>46,38%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,0%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>362995</t>
+          <t>367049</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>417492</t>
+          <t>421137</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,57%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>464689</t>
+          <t>465035</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>527665</t>
+          <t>529265</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>845106</t>
+          <t>850566</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>930724</t>
+          <t>932760</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>53,62%</t>
+          <t>53,74%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>659751</t>
+          <t>659628</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>751421</t>
+          <t>751159</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>647347</t>
+          <t>644519</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>731035</t>
+          <t>729920</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1327479</t>
+          <t>1328114</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1459300</t>
+          <t>1452873</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,0%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1306851</t>
+          <t>1307113</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1398521</t>
+          <t>1398644</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1246769</t>
+          <t>1247884</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1330457</t>
+          <t>1333285</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>63,09%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>2576777</t>
+          <t>2583204</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2708598</t>
+          <t>2707963</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,09%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44998</t>
+          <t>45120</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>76176</t>
+          <t>74402</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>13,65%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>60957</t>
+          <t>60941</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>93692</t>
+          <t>94128</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4680,7 +4680,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>115871</t>
+          <t>115437</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>159996</t>
+          <t>159988</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>468803</t>
+          <t>470577</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>499981</t>
+          <t>499859</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>86,02%</t>
+          <t>86,35%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>454384</t>
+          <t>453948</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>487119</t>
+          <t>487135</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,91%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>933059</t>
+          <t>933067</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>977184</t>
+          <t>977618</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4828,7 +4828,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>89,4%</t>
+          <t>89,44%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1062183</t>
+          <t>1061049</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1172666</t>
+          <t>1176044</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1197515</t>
+          <t>1201388</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1313839</t>
+          <t>1321203</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2292824</t>
+          <t>2296136</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2451188</t>
+          <t>2457823</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,71%</t>
+          <t>35,8%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2177884</t>
+          <t>2174506</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2288367</t>
+          <t>2289501</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2200512</t>
+          <t>2193148</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2316836</t>
+          <t>2312963</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>62,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4413713</t>
+          <t>4407078</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4572077</t>
+          <t>4568765</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,29%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,6%</t>
+          <t>66,55%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>135238</t>
+          <t>163287</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>117461</t>
+          <t>143102</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>154640</t>
+          <t>185261</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>32,74%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>202715</t>
+          <t>227045</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>184883</t>
+          <t>206853</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>223749</t>
+          <t>247830</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>25,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>337953</t>
+          <t>390332</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>311551</t>
+          <t>363148</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>366728</t>
+          <t>419549</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>30,48%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>369407</t>
+          <t>402646</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>350005</t>
+          <t>380672</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>387184</t>
+          <t>422831</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>540327</t>
+          <t>583314</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>519293</t>
+          <t>562529</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>558159</t>
+          <t>603506</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,72%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>69,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>74,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>909734</t>
+          <t>985959</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>880959</t>
+          <t>956742</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>936136</t>
+          <t>1013143</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>71,64%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,03%</t>
+          <t>73,61%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>504645</t>
+          <t>565933</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>504645</t>
+          <t>565933</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>504645</t>
+          <t>565933</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>743042</t>
+          <t>810359</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>743042</t>
+          <t>810359</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>743042</t>
+          <t>810359</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1247687</t>
+          <t>1376291</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1247687</t>
+          <t>1376291</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1247687</t>
+          <t>1376291</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>262032</t>
+          <t>313193</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>178814</t>
+          <t>277160</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>311258</t>
+          <t>352160</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>371003</t>
+          <t>354800</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>283945</t>
+          <t>324064</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>577725</t>
+          <t>394914</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>633035</t>
+          <t>667993</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>518905</t>
+          <t>622083</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>852269</t>
+          <t>722187</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>19,13%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2000124</t>
+          <t>1886234</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1950898</t>
+          <t>1847267</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2083342</t>
+          <t>1922267</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>87,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>1822569</t>
+          <t>1802746</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1615847</t>
+          <t>1762632</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1909627</t>
+          <t>1833482</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>81,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>3822693</t>
+          <t>3688980</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3603459</t>
+          <t>3634786</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3936823</t>
+          <t>3734890</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>85,79%</t>
+          <t>84,67%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,87%</t>
+          <t>83,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>85,72%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2262156</t>
+          <t>2199427</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2262156</t>
+          <t>2199427</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2262156</t>
+          <t>2199427</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2193572</t>
+          <t>2157546</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2193572</t>
+          <t>2157546</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2193572</t>
+          <t>2157546</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4455728</t>
+          <t>4356973</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4455728</t>
+          <t>4356973</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4455728</t>
+          <t>4356973</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17128</t>
+          <t>22260</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9928</t>
+          <t>13656</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29286</t>
+          <t>36574</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>33851</t>
+          <t>41735</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>25511</t>
+          <t>30519</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45616</t>
+          <t>55494</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>50979</t>
+          <t>63995</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>38771</t>
+          <t>49706</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65834</t>
+          <t>82705</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>625690</t>
+          <t>685217</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>613532</t>
+          <t>670903</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>632890</t>
+          <t>693821</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>96,85%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>617247</t>
+          <t>681858</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>605482</t>
+          <t>668099</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>625587</t>
+          <t>693074</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,8%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1242937</t>
+          <t>1367075</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1228082</t>
+          <t>1348365</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1255145</t>
+          <t>1381364</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,53%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>642818</t>
+          <t>707477</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>642818</t>
+          <t>707477</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>642818</t>
+          <t>707477</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>651098</t>
+          <t>723593</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>651098</t>
+          <t>723593</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>651098</t>
+          <t>723593</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1293916</t>
+          <t>1431070</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1293916</t>
+          <t>1431070</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1293916</t>
+          <t>1431070</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>414398</t>
+          <t>498739</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>316599</t>
+          <t>450681</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>465255</t>
+          <t>542953</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>12,15%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>607568</t>
+          <t>623580</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>515803</t>
+          <t>581195</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>822901</t>
+          <t>661527</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>1021966</t>
+          <t>1122320</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>890887</t>
+          <t>1061168</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1208023</t>
+          <t>1183409</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>16,52%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2995222</t>
+          <t>2974098</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2944365</t>
+          <t>2929884</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3093021</t>
+          <t>3022156</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>87,85%</t>
+          <t>85,64%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>2980144</t>
+          <t>3067917</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2764811</t>
+          <t>3029970</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3071909</t>
+          <t>3110302</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>83,07%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,62%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>5975365</t>
+          <t>6042014</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5789308</t>
+          <t>5980925</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6106444</t>
+          <t>6103166</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>85,39%</t>
+          <t>84,33%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>83,48%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>85,19%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3409620</t>
+          <t>3472837</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3409620</t>
+          <t>3472837</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3409620</t>
+          <t>3472837</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3587712</t>
+          <t>3691497</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3587712</t>
+          <t>3691497</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3587712</t>
+          <t>3691497</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6997331</t>
+          <t>7164334</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6997331</t>
+          <t>7164334</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6997331</t>
+          <t>7164334</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
